--- a/data/trans_camb/P1001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,88</t>
+          <t>-3,02; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,35</t>
+          <t>-2,14; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,54</t>
+          <t>-1,64; 4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,71</t>
+          <t>-3,7; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 4,35</t>
+          <t>-3,91; 3,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,29</t>
+          <t>-3,45; 4,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,72</t>
+          <t>-2,12; 2,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,93</t>
+          <t>-2,04; 2,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,4</t>
+          <t>-1,05; 3,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 99,26</t>
+          <t>-53,52; 107,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 112,73</t>
+          <t>-38,56; 112,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 153,76</t>
+          <t>-31,11; 145,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 94,87</t>
+          <t>-43,47; 98,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 92,59</t>
+          <t>-45,1; 82,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 96,67</t>
+          <t>-36,61; 88,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 65,06</t>
+          <t>-34,36; 62,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 66,84</t>
+          <t>-30,43; 64,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 79,31</t>
+          <t>-15,81; 86,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,67</t>
+          <t>-1,3; 5,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,82</t>
+          <t>-2,48; 3,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,69</t>
+          <t>-4,62; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,17</t>
+          <t>-3,21; 5,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,25</t>
+          <t>-5,87; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,99</t>
+          <t>-2,9; 4,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,03</t>
+          <t>-1,71; 3,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,93</t>
+          <t>-3,29; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,58</t>
+          <t>-3,37; 1,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 204,13</t>
+          <t>-27,31; 207,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 135,96</t>
+          <t>-43,05; 144,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 34,07</t>
+          <t>-72,74; 41,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 77,85</t>
+          <t>-32,33; 87,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 39,94</t>
+          <t>-57,56; 25,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 75,82</t>
+          <t>-27,32; 74,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 81,26</t>
+          <t>-22,37; 72,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 40,5</t>
+          <t>-41,85; 36,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 32,62</t>
+          <t>-42,16; 29,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,36</t>
+          <t>-0,78; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,12</t>
+          <t>-2,02; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,71</t>
+          <t>-6,25; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 13,4</t>
+          <t>-0,45; 14,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 10,88</t>
+          <t>-4,73; 10,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 5,59</t>
+          <t>-6,76; 5,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,94</t>
+          <t>1,37; 7,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,28</t>
+          <t>-1,91; 4,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 2,57</t>
+          <t>-5,84; 2,59</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 109,76</t>
+          <t>-12,46; 112,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 86,56</t>
+          <t>-27,46; 85,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 45,99</t>
+          <t>-73,15; 61,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 178,37</t>
+          <t>-6,37; 188,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 145,24</t>
+          <t>-35,27; 152,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 79,57</t>
+          <t>-43,17; 76,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 111,62</t>
+          <t>13,89; 118,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 72,08</t>
+          <t>-21,71; 69,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,35; 36,5</t>
+          <t>-65,96; 37,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,95; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,18</t>
+          <t>-3,99; 0,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,02</t>
+          <t>-3,17; 1,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,28</t>
+          <t>-0,68; 6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,54</t>
+          <t>-0,75; 5,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,24</t>
+          <t>-7,27; 0,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,87</t>
+          <t>-0,03; 3,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,59</t>
+          <t>-1,72; 1,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; -0,06</t>
+          <t>-4,44; -0,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 54,04</t>
+          <t>-11,53; 57,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 2,51</t>
+          <t>-45,13; 2,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 14,98</t>
+          <t>-36,73; 16,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 77,49</t>
+          <t>-6,46; 75,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 69,31</t>
+          <t>-7,05; 68,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 0,89</t>
+          <t>-64,16; 2,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 49,33</t>
+          <t>-0,31; 48,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 21,72</t>
+          <t>-18,77; 21,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -1,52</t>
+          <t>-46,66; -1,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,66</t>
+          <t>-4,39; 2,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,04</t>
+          <t>-1,44; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,64</t>
+          <t>-1,51; 5,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 13,81</t>
+          <t>6,26; 14,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,78</t>
+          <t>3,02; 10,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 7,3</t>
+          <t>-1,06; 7,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,22</t>
+          <t>2,84; 8,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,14</t>
+          <t>1,67; 7,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,64</t>
+          <t>-0,11; 5,83</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 63,53</t>
+          <t>-50,43; 59,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 114,55</t>
+          <t>-18,25; 141,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 135,77</t>
+          <t>-22,2; 134,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51,11; 175,66</t>
+          <t>50,89; 180,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,43; 140,27</t>
+          <t>24,74; 138,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 90,56</t>
+          <t>-8,82; 89,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,38; 116,46</t>
+          <t>28,43; 130,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,52; 100,66</t>
+          <t>16,7; 100,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,86; 80,65</t>
+          <t>-1,64; 81,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,34</t>
+          <t>-3,26; 3,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,22</t>
+          <t>-3,07; 3,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,63</t>
+          <t>-3,09; 5,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,78</t>
+          <t>3,25; 8,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,28</t>
+          <t>0,49; 6,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,42</t>
+          <t>2,94; 8,68</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,07</t>
+          <t>2,38; 6,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,83</t>
+          <t>0,18; 4,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,25</t>
+          <t>1,53; 6,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 157,7</t>
+          <t>-63,67; 150,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 152,37</t>
+          <t>-61,2; 152,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 283,05</t>
+          <t>-67,29; 222,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,69; 103,8</t>
+          <t>29,54; 100,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,05; 74,6</t>
+          <t>4,68; 70,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,06; 98,22</t>
+          <t>25,51; 99,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,26; 92,37</t>
+          <t>24,31; 91,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,09; 62,68</t>
+          <t>1,57; 63,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,39; 80,28</t>
+          <t>14,96; 79,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,27</t>
+          <t>-0,31; 2,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,3</t>
+          <t>-1,2; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,78</t>
+          <t>-1,93; 0,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,84</t>
+          <t>3,69; 6,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,42</t>
+          <t>1,38; 4,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,05</t>
+          <t>-0,93; 2,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,2</t>
+          <t>2,13; 4,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,45</t>
+          <t>0,45; 2,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,45</t>
+          <t>-0,82; 1,67</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 41,65</t>
+          <t>-4,81; 39,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 24,39</t>
+          <t>-18,11; 24,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 13,87</t>
+          <t>-30,23; 14,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37,08; 78,7</t>
+          <t>36,0; 79,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,89; 51,1</t>
+          <t>12,81; 50,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 35,31</t>
+          <t>-8,71; 31,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,89; 57,98</t>
+          <t>25,6; 57,39</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,33; 33,87</t>
+          <t>5,29; 32,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 19,83</t>
+          <t>-9,6; 22,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,94</t>
+          <t>-2,87; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,21</t>
+          <t>-2,39; 3,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,52</t>
+          <t>-1,88; 4,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,73</t>
+          <t>-3,22; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,99</t>
+          <t>-3,96; 4,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,01</t>
+          <t>-3,23; 4,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,78</t>
+          <t>-2,01; 2,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,74</t>
+          <t>-1,96; 2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,52</t>
+          <t>-1,14; 3,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 107,23</t>
+          <t>-53,01; 94,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 112,96</t>
+          <t>-44,23; 107,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 145,4</t>
+          <t>-34,06; 129,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 98,39</t>
+          <t>-38,18; 102,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 82,19</t>
+          <t>-44,63; 85,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 88,88</t>
+          <t>-33,97; 91,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 62,42</t>
+          <t>-31,41; 62,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 64,4</t>
+          <t>-30,33; 67,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 86,5</t>
+          <t>-18,85; 78,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,81</t>
+          <t>-1,53; 5,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,76</t>
+          <t>-2,49; 4,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,87</t>
+          <t>-4,36; 1,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,67</t>
+          <t>-3,62; 4,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,42</t>
+          <t>-6,42; 1,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,77</t>
+          <t>-3,11; 4,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,79</t>
+          <t>-1,47; 3,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,94</t>
+          <t>-3,35; 2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,47</t>
+          <t>-2,79; 2,06</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-38,94%</t>
+          <t>-35,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,41%</t>
+          <t>-6,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 207,91</t>
+          <t>-30,32; 194,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 144,09</t>
+          <t>-41,36; 153,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 41,05</t>
+          <t>-69,05; 60,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 87,61</t>
+          <t>-35,35; 69,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 25,48</t>
+          <t>-59,06; 28,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 74,29</t>
+          <t>-27,43; 76,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 72,32</t>
+          <t>-20,24; 77,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 36,43</t>
+          <t>-42,41; 41,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 29,21</t>
+          <t>-36,3; 45,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>1,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,76</t>
+          <t>-0,85; 5,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,8</t>
+          <t>-2,27; 3,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,36</t>
+          <t>-1,91; 4,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 14,22</t>
+          <t>-0,31; 13,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 10,71</t>
+          <t>-4,93; 11,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,63</t>
+          <t>-7,12; 5,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,04</t>
+          <t>0,94; 7,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,12</t>
+          <t>-1,86; 4,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 2,59</t>
+          <t>-1,8; 4,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-16,13%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,77%</t>
+          <t>-3,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-14,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 112,49</t>
+          <t>-11,66; 116,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 85,18</t>
+          <t>-31,82; 84,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 61,35</t>
+          <t>-27,83; 95,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 188,9</t>
+          <t>-3,38; 190,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 152,37</t>
+          <t>-35,05; 153,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 76,43</t>
+          <t>-46,26; 73,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 118,37</t>
+          <t>10,36; 117,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 69,11</t>
+          <t>-20,18; 74,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 37,67</t>
+          <t>-20,0; 66,14</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,81</t>
+          <t>-1,16; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,2</t>
+          <t>-3,83; 0,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,02</t>
+          <t>-3,05; 0,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,13</t>
+          <t>-0,47; 6,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,39</t>
+          <t>-1,2; 5,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 0,28</t>
+          <t>-3,94; 1,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,7</t>
+          <t>-0,06; 3,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,56</t>
+          <t>-1,95; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,08</t>
+          <t>-2,58; 0,75</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-15,71%</t>
+          <t>-15,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,21%</t>
+          <t>-10,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,85%</t>
+          <t>-11,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 57,51</t>
+          <t>-13,94; 52,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 2,94</t>
+          <t>-43,81; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 16,28</t>
+          <t>-34,54; 12,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 75,79</t>
+          <t>-4,6; 75,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 68,08</t>
+          <t>-11,08; 62,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 2,34</t>
+          <t>-33,37; 21,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 48,65</t>
+          <t>-0,66; 49,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 21,02</t>
+          <t>-21,06; 19,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,66; -1,3</t>
+          <t>-27,8; 9,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,56</t>
+          <t>-4,19; 2,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,53</t>
+          <t>-1,42; 5,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,85</t>
+          <t>-2,57; 4,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,34</t>
+          <t>6,27; 13,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,75</t>
+          <t>3,35; 10,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,12</t>
+          <t>1,33; 8,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,89</t>
+          <t>3,13; 8,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,11</t>
+          <t>1,78; 6,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 5,83</t>
+          <t>1,02; 5,54</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 59,55</t>
+          <t>-47,36; 67,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 141,78</t>
+          <t>-17,31; 136,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 134,08</t>
+          <t>-30,39; 101,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50,89; 180,67</t>
+          <t>48,64; 173,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,74; 138,96</t>
+          <t>27,58; 131,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 89,31</t>
+          <t>10,48; 104,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,43; 130,76</t>
+          <t>31,3; 121,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,7; 100,24</t>
+          <t>16,57; 97,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 81,32</t>
+          <t>10,11; 79,61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,36</t>
+          <t>-3,36; 3,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,31</t>
+          <t>-3,14; 3,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,21</t>
+          <t>-2,5; 6,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,49</t>
+          <t>3,35; 8,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,04</t>
+          <t>0,7; 5,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,68</t>
+          <t>2,5; 7,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,94</t>
+          <t>2,49; 6,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,8</t>
+          <t>0,19; 4,83</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,35</t>
+          <t>1,77; 6,59</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,67; 150,24</t>
+          <t>-63,97; 137,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 152,31</t>
+          <t>-61,24; 148,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 222,19</t>
+          <t>-61,86; 266,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29,54; 100,17</t>
+          <t>29,62; 98,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,68; 70,57</t>
+          <t>6,57; 69,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,51; 99,08</t>
+          <t>23,31; 92,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,31; 91,89</t>
+          <t>25,65; 87,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,57; 63,99</t>
+          <t>2,01; 63,7</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,96; 79,97</t>
+          <t>18,7; 86,53</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,21</t>
+          <t>-0,23; 2,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,31</t>
+          <t>-1,16; 1,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,82</t>
+          <t>-1,24; 1,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,93</t>
+          <t>3,55; 6,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,39</t>
+          <t>1,36; 4,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,75</t>
+          <t>0,82; 3,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,12</t>
+          <t>2,08; 4,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,43</t>
+          <t>0,54; 2,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,67</t>
+          <t>0,07; 1,95</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,82%</t>
+          <t>-1,96%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 39,19</t>
+          <t>-3,69; 42,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 24,01</t>
+          <t>-17,86; 22,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 14,39</t>
+          <t>-18,82; 21,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36,0; 79,42</t>
+          <t>35,9; 78,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,81; 50,14</t>
+          <t>13,48; 51,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 31,47</t>
+          <t>7,98; 42,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,6; 57,39</t>
+          <t>25,68; 56,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,29; 32,54</t>
+          <t>6,49; 34,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 22,85</t>
+          <t>0,56; 26,64</t>
         </is>
       </c>
     </row>
